--- a/branches/fix/go-publish-bootstrap/StructureDefinition-mii-pr-biobank-specimen-core.xlsx
+++ b/branches/fix/go-publish-bootstrap/StructureDefinition-mii-pr-biobank-specimen-core.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc2</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-02</t>
+    <t>2026-09-10</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -636,7 +636,7 @@
 </t>
   </si>
   <si>
-    <t>Infektiositätsstatus</t>
+    <t>MII EX Biobank Infektiositätsstatus</t>
   </si>
   <si>
     <t>Extension zur Angabe des Infektiositätsstatus einer Probe anhand der Biosafety-Level-Einstufung (BSL-1 bis BSL-4, SNOMED CT) bzw. der Angabe, dass keine Infektionsgefahr bekannt ist.</t>
@@ -14336,7 +14336,7 @@
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G112" t="s" s="2">
         <v>77</v>
@@ -14442,7 +14442,7 @@
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G113" t="s" s="2">
         <v>83</v>
@@ -17992,7 +17992,7 @@
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G146" t="s" s="2">
         <v>83</v>
